--- a/26-08_August_Metadata.xlsx
+++ b/26-08_August_Metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://asprsorg-my.sharepoint.com/personal/maustin_asprs_org/Documents/PERS/2026 PERS/2026 PERS Metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="154" documentId="8_{5EE3A922-ABA0-43D0-A9B5-4D5B4955916C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B4A9054-5E6D-415D-A084-3E87D8350527}"/>
+  <xr:revisionPtr revIDLastSave="160" documentId="8_{5EE3A922-ABA0-43D0-A9B5-4D5B4955916C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A859F21-85BA-4D91-AB1F-E5D4161D7EF6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ED1827D4-DBB2-442E-8398-F081D1A3FEC4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="380">
   <si>
     <t>Manuscript No.</t>
   </si>
@@ -1131,6 +1131,54 @@
   </si>
   <si>
     <t>26-00024R2</t>
+  </si>
+  <si>
+    <t>Accuracy; DEM; DTM; Geomorphometry</t>
+  </si>
+  <si>
+    <t>Modern digital elevation models (DEMs) are generated with increasingly small cell sizes and high accuracy, yet no closed-form relationship links these variables. Previous work relied on empirical formulations validated experimentally. This paper derives an analytical relationship for the traditional elevation mean square error (MSE) accuracy metric and highlights limitations of empirical approaches. Common practice wrongly dismisses the effect of the choice of interpolation method on DEM accuracy. Accuracy reports may even fail to mention which interpolation method was used. The analysis was limited to two local interpolation methods: nearest neighbor and bilinear interpolation. In those cases we show that the model accuracy is bounded by three terms: one depending only on the dataset elevation MSE; mixed monomials depending on both the dataset elevation MSE and powers of the cell size h; and a term independent of the dataset elevation MSE and proportional to a power of h. For a given interpolation method, the exponents of h are constant, whereas the coefficients can be estimated from local terrain characteristics at the control points. For bilinear interpolation, the exponents are twice those for nearest-neighbor interpolation. The availability of this analytical relationship makes it possible to determine the cell size or instrument accuracy required to achieve a specified target DEM accuracy. Because the result depends strongly on the interpolation method, the recommended interpolation method should be routinely and explicitly mentioned in the DEM producer’s accuracy report</t>
+  </si>
+  <si>
+    <t>10.14358/PERS.26-00035R4</t>
+  </si>
+  <si>
+    <t>Laboratorio LatinGEO IGM+ORT, Universidad ORT Uruguay</t>
+  </si>
+  <si>
+    <t>López-Vázquez, Carlos</t>
+  </si>
+  <si>
+    <t>Analytical Estimate of Digital Elevation Model Accuracy (Mean Square Error) as a Function of Cell Size and Dataset Elevation Error</t>
+  </si>
+  <si>
+    <t>26-00035R4</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1JSDqD2z0efejUWCbiq-5f3__RyOk3X2P/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1bm3omvM5Y1ZxSE-BkVRCKh7ONw2eBIE0/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Domain adaptation, remote sensing, scene classification, contrastive learning</t>
+  </si>
+  <si>
+    <t>Cross-domain remote sensing scene classification suffers from severe domain shifts caused by sensor and geographic variations. Existing adversarial domain adaptation methods mainly align global feature distributions but often neglect category-level structure, leading to ambiguous decision boundaries in the target domain. In this paper, we propose a neighborhood geometry–guided prototype contrastive adaptation (NGPCA) framework built upon the domain-adversarial neural network. The proposed method leverages local neighborhood geometry in the target feature space to construct neighborhood-consensus pseudo labels and further introduces prototype contrastive learning to align target features with source-domain class prototypes. By combining neighborhood consensus supervision with prototype-level contrastive adaptation, NGPCA improves pseudo-label robustness and promotes more discriminative feature learning. Extensive experiments on University of California, Merced land-use data set, the Aerial Image Data Set, and the NWPU-RESISC45 data set with six cross-domain transfer tasks demonstrate the effectiveness of the proposed framework. NGPCA achieves the best average accuracy of 98.26% among the compared remote sensing–oriented and general domain adaptation methods, showing robust performance for cross-domain remote sensing scene classification.</t>
+  </si>
+  <si>
+    <t>10.14358/PERS.26-00048R3</t>
+  </si>
+  <si>
+    <t>1: School of Geography and Spatial Information Sciences, Jiangsu Normal University, Xuzhou, China 2: Shandong Provincial Institute of Land Surveying and Mapping, Jinan, China</t>
+  </si>
+  <si>
+    <t>He, Qing 1 ; Li, Erzhu 1 ; Zhu, Wei 2 ; Wang, Yongqing 1 ; </t>
+  </si>
+  <si>
+    <t>Neighborhood Geometry–Guided Prototype Contrastive Adaptation for Cross-Domain Remote Sensing Scene Classification</t>
+  </si>
+  <si>
+    <t>26-00048R3</t>
   </si>
 </sst>
 </file>
@@ -1712,7 +1760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8FD8486-47DD-4802-9EE8-87FBEF8AE4F5}">
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:S46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -3501,6 +3549,90 @@
       <c r="Q44" s="25"/>
       <c r="R44" s="25"/>
     </row>
+    <row r="45" spans="1:18" ht="195" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B45" s="15"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="O45" s="5"/>
+      <c r="P45" s="26"/>
+      <c r="Q45" s="26"/>
+      <c r="R45" s="23"/>
+    </row>
+    <row r="46" spans="1:18" ht="165" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B46" s="15"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="O46" s="5"/>
+      <c r="P46" s="26"/>
+      <c r="Q46" s="26"/>
+      <c r="R46" s="23"/>
+    </row>
   </sheetData>
   <autoFilter ref="E1:E13" xr:uid="{D8FD8486-47DD-4802-9EE8-87FBEF8AE4F5}"/>
   <hyperlinks>

--- a/26-08_August_Metadata.xlsx
+++ b/26-08_August_Metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://asprsorg-my.sharepoint.com/personal/maustin_asprs_org/Documents/PERS/2026 PERS/2026 PERS Metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="160" documentId="8_{5EE3A922-ABA0-43D0-A9B5-4D5B4955916C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A859F21-85BA-4D91-AB1F-E5D4161D7EF6}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="8_{5EE3A922-ABA0-43D0-A9B5-4D5B4955916C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5359F03D-5464-4629-8E8E-7CA4825D75BD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ED1827D4-DBB2-442E-8398-F081D1A3FEC4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="395">
   <si>
     <t>Manuscript No.</t>
   </si>
@@ -1179,6 +1179,51 @@
   </si>
   <si>
     <t>26-00048R3</t>
+  </si>
+  <si>
+    <t>26-00025R2</t>
+  </si>
+  <si>
+    <t>Song, Shuang; Kim, Jiyong; Qin, Rongjun</t>
+  </si>
+  <si>
+    <t>Geospatial Data Analytics Laboratory, Department of Civil, Environmental and Geodetic Engineering, The Ohio State University</t>
+  </si>
+  <si>
+    <t>10.14358/PERS.26-00025R2</t>
+  </si>
+  <si>
+    <t>High-resolution satellite imagery demands three-dimensional (3D) reconstruction methods that deliver both speed and geometric accuracy. Recent adaptations of 3D Gaussian splatting (3DGS) to satellite imagery demonstrate strong efficiency, but reconstruction quality often degrades under diverse illumination across multi-date, high-altitude acquisitions (with small intersection angles), limiting applicability to remote sensing and vision tasks. We present SatSplat, the first framework to adapt 2D Gaussian splatting (2DGS) to satellite photogrammetry, with online camera adjustment. We approximated satellite cameras with an affine model and learned a minimal delta parameterization for in-splat camera refinement from dense observations. The formulation was implemented with a 2DGS scene representation. To handle time-varying shadows and illumination changes, we integrated geometric shadow mapping and per-camera color correction during training. Across the evaluated DFC2019 and IARPA2016 benchmark sites, SatSplat achieved strong geometric accuracy while significantly outperforming prior 3DGS-based baselines. On our processed DFC2019 benchmark, SatSplat reduced mean absolute error by 11.93% and peak video memory by 31% relative to the previous state of the art. Our approach enabled large-scale digital surface modeling with practical computational efficiency. The project page is available at https://gdaosu.github.io/satsplat.</t>
+  </si>
+  <si>
+    <t>2D Gaussian Splatting (2DGS); Satellite Photogrammetry; 3D Reconstruction; Affine Camera Model; Surface Modeling; Geometric Shadow Mapping; Multi-Date Imagery</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1cWVJZ5vz-ZPPqZn1MTo3edlLVuoMo1KJ/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1CtBnoZzmRO5hdIu12TBVVSdcqTfrWXAl/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>object detection; remote sensing images (RSIs); spatial-spectral collaborative fusion; sparse attention; four-scale detection head</t>
+  </si>
+  <si>
+    <t>Remote sensing object detection (RSOD) remains highly challenging due to large variations in object scale, dense distributions of tiny targets, spectral similarity between targets and complex land-cover backgrounds, cross-domain heterogeneous noise interference, and blurred object boundaries. To address these issues, this paper proposes spatial–spectral synergistic and sparse global-aware (SSSG)–YOLO, a novel RSOD framework built upon spatio-spectral collaboration and sparse global perception. Specifically, a four-scale detection head is constructed to retain high-resolution shallow features, thereby alleviating the loss of tiny-object information during downsampling. To mitigate aliasing in feature fusion, an adaptive spatio-spectral synergizer is designed to dynamically align the spatial and spectral information of multi-scale features via frequency-domain decoupling. Furthermore, to compensate for insufficient deep semantic modeling, a sparse global context module, namely C3TR–blockwise random sparse attention, is introduced to capture long-range dependencies while reducing computational redundancy. In addition, a hierarchical dual-path attention (HDPA) module is deployed at the end of the neck, immediately preceding the detection head, to refine the fused multi-scale features. Through cascaded enhancement, HDPA improves the saliency of low-contrast targets and suppresses background noise, providing the detection head with high signal-to-noise ratio input features. Extensive experiments on three public data sets, namely RSOD, DIOR, and VisDrone-DET2019, demonstrate the effectiveness of the proposed method. SSSG-YOLO achieves mean average precision scores of 96.1%, 89.8%, and 39.0% on the RSOD, DIOR, and VisDrone-DET2019 data sets, respectively.</t>
+  </si>
+  <si>
+    <t>10.14358/PERS.26-00064R3</t>
+  </si>
+  <si>
+    <t>School of Artificial Intelligence and Big Data, Hefei University</t>
+  </si>
+  <si>
+    <t>Chen, Yan; Wang, Jinhong; Wang, Xiaofeng; Xu, Hao; Zhang, Chen; Xu, Lixiang</t>
+  </si>
+  <si>
+    <t>SSSG-YOLO: Spatial–Spectral Synergistic and Sparse Global-Aware Network for Remote Sensing Object Detection</t>
+  </si>
+  <si>
+    <t>26-00064R3</t>
   </si>
 </sst>
 </file>
@@ -1760,7 +1805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8FD8486-47DD-4802-9EE8-87FBEF8AE4F5}">
-  <dimension ref="A1:S46"/>
+  <dimension ref="A1:S48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -3633,6 +3678,87 @@
       <c r="Q46" s="26"/>
       <c r="R46" s="23"/>
     </row>
+    <row r="47" spans="1:18" ht="180" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B47" s="15"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="O47" s="5"/>
+      <c r="P47" s="26"/>
+      <c r="Q47" s="26"/>
+      <c r="R47" s="23"/>
+    </row>
+    <row r="48" spans="1:18" ht="210" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B48" s="15"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="O48" s="5"/>
+      <c r="P48" s="26"/>
+      <c r="Q48" s="26"/>
+      <c r="R48" s="23"/>
+    </row>
   </sheetData>
   <autoFilter ref="E1:E13" xr:uid="{D8FD8486-47DD-4802-9EE8-87FBEF8AE4F5}"/>
   <hyperlinks>

--- a/26-08_August_Metadata.xlsx
+++ b/26-08_August_Metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://asprsorg-my.sharepoint.com/personal/maustin_asprs_org/Documents/PERS/2026 PERS/2026 PERS Metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="8_{5EE3A922-ABA0-43D0-A9B5-4D5B4955916C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5359F03D-5464-4629-8E8E-7CA4825D75BD}"/>
+  <xr:revisionPtr revIDLastSave="165" documentId="8_{5EE3A922-ABA0-43D0-A9B5-4D5B4955916C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CAEF8C5-BA25-4A73-9D67-A4705E3AECAE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ED1827D4-DBB2-442E-8398-F081D1A3FEC4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="411">
   <si>
     <t>Manuscript No.</t>
   </si>
@@ -1224,6 +1224,54 @@
   </si>
   <si>
     <t>26-00064R3</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rYGxjmumyqXopG10vagxLYg_iaguBHcA/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>change detection, weakly supervised learning, point annotations, SAM</t>
+  </si>
+  <si>
+    <t>Point-based weakly supervised strategies can reduce annotation costs but suffer from the problems of semantic sparsity and boundary ambiguity. This paper proposes an uncertainty-aware weakly supervised building change detection method with point annotations. First, the method leverages the proposal generation capability and embedding space of the Segment Anything model to generate reliable three-class pseudo-labels. By fusing appearance similarity and geometric overlap at the proposal level, it distinguishes high-confidence changed/no-change regions and uncertain regions, which not only enriches the semantic information of annotations but also mitigates the prompt-induced semantic bias. Then, an entropy minimization strategy is adopted to impose constraints on low-confidence uncertain pixels, which suppresses noisy supervision while achieving refined boundary extraction. To verify the effectiveness of the proposed method, experiments on standard building change detection benchmark data sets show that compared with existing weakly supervised methods, the proposal-level matching strategy significantly improves the fidelity of pseudo-labels, thus yielding more robust and accurate change detection results.</t>
+  </si>
+  <si>
+    <t>10.14358/PERS.26-00046R5</t>
+  </si>
+  <si>
+    <t>1: School of Geography, Geomatics and Planning, Jiangsu Normal University 2: Shandong Provincial Institute of Land Surveying and Mapping</t>
+  </si>
+  <si>
+    <t>Wang, Yongqing 1 ; Li, Erzhu 1 ; Du, Lihua 2 ; He, Qing 1 ; </t>
+  </si>
+  <si>
+    <t>Uncertainty-Aware Weakly Supervised Building Change Detection with Point Annotations</t>
+  </si>
+  <si>
+    <t>26-00046R5</t>
+  </si>
+  <si>
+    <t>Seabed monitoring; Shoreline change; Sediment dynamics; Hel Peninsula</t>
+  </si>
+  <si>
+    <t>This study presents a pilot, data-driven framework for detecting nearshore seabed dynamics based on shoreline variability derived from high-resolution satellite imagery, integrated with in situ bathymetric measurements along the Hel Peninsula in the southern Baltic Sea. The approach focuses on assessing whether satellite-derived shoreline displacement can serve as an indirect indicator of changes in seabed morphology within the sedimentologically active coastal zone. Four cross-shore transects were analyzed using Pléiades satellite imagery and field bathymetric data collected during two monitoring campaigns conducted in 2019 and 2022. Changes in seabed elevation were quantified through cross-sectional profile analysis, while key morphodynamic parameters, including closure depth and the length of the active seabed, were estimated using empirical formulations proposed by Hallermeier, Birkemeier, and Houston. To provide hydrodynamic context, wave and current conditions were characterized using Copernicus Marine Service reanalysis data. The results reveal pronounced spatial variability in seabed response along the Hel Peninsula, with erosion-dominated conditions in high-energy open-coast sectors and limited morphological change in semienclosed, low-energy environments. Among the tested formulations, Birkemeier’s equation showed the closest agreement with field-derived closure depths, while all empirical models systematically overestimated closure depth in low-energy settings. The findings demonstrate the potential of satellite-based shoreline observations as a supporting tool for coastal morphodynamic assessment while highlighting the limitations imposed by measurement uncertainty, short observation windows, and simplified process representation. Overall, the proposed framework should be regarded as a proof-of-concept application requiring longer observational time series, improved uncertainty quantification, and local calibration before operational implementation can be considered</t>
+  </si>
+  <si>
+    <t>10.14358/PERS.26-00037R4</t>
+  </si>
+  <si>
+    <t>Institute of Meteorology and Water Management National Research Institute</t>
+  </si>
+  <si>
+    <t>Sapiega, Patryk; Zalewska, Tamara</t>
+  </si>
+  <si>
+    <t>Satellite-Based Framework for Detecting Seabed Dynamics from Shoreline Variability along Spit Coasts—A Pilot Study from the Hel Peninsula</t>
+  </si>
+  <si>
+    <t>26-00037R4</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/12kTtQZfL5TLylCH5WowXwzI85DwAl-mn/view?usp=drive_link</t>
   </si>
 </sst>
 </file>
@@ -1482,10 +1530,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1805,7 +1849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8FD8486-47DD-4802-9EE8-87FBEF8AE4F5}">
-  <dimension ref="A1:S48"/>
+  <dimension ref="A1:S50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -3759,6 +3803,89 @@
       <c r="Q48" s="26"/>
       <c r="R48" s="23"/>
     </row>
+    <row r="49" spans="1:18" ht="150" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B49" s="15"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="O49" s="5"/>
+      <c r="P49" s="26"/>
+      <c r="Q49" s="23"/>
+      <c r="R49" s="23"/>
+    </row>
+    <row r="50" spans="1:18" ht="240" x14ac:dyDescent="0.25">
+      <c r="B50" s="15">
+        <v>46255</v>
+      </c>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="O50" s="5"/>
+      <c r="P50" s="23"/>
+      <c r="Q50" s="23"/>
+      <c r="R50" s="23"/>
+    </row>
   </sheetData>
   <autoFilter ref="E1:E13" xr:uid="{D8FD8486-47DD-4802-9EE8-87FBEF8AE4F5}"/>
   <hyperlinks>

--- a/26-08_August_Metadata.xlsx
+++ b/26-08_August_Metadata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://asprsorg-my.sharepoint.com/personal/maustin_asprs_org/Documents/PERS/2026 PERS/2026 PERS Metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="165" documentId="8_{5EE3A922-ABA0-43D0-A9B5-4D5B4955916C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CAEF8C5-BA25-4A73-9D67-A4705E3AECAE}"/>
+  <xr:revisionPtr revIDLastSave="170" documentId="8_{5EE3A922-ABA0-43D0-A9B5-4D5B4955916C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F9A554C-425E-43C7-B91A-216C2A0EDFBE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ED1827D4-DBB2-442E-8398-F081D1A3FEC4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="435">
   <si>
     <t>Manuscript No.</t>
   </si>
@@ -1272,6 +1272,78 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/12kTtQZfL5TLylCH5WowXwzI85DwAl-mn/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1HG30JkNg0p5o7f3Ww3h0ByicNX3oEd7r/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Visual-LiDAR, 3D Gaussian Splatting, SLAM</t>
+  </si>
+  <si>
+    <t>Recent studies highlight the effectiveness of 3D Gaussian splatting (3DGS) in visual simultaneous localization and mapping (SLAM) systems, which work well indoors but struggle in large-scale outdoor environments. Typically, lidar data are used to address this issue; however, current multi-modal SLAM systems use 3DGS mainly for mapping, leaving its potential to enhance tracking unexplored. In this paper, we present VLGS-SLAM, a novel visual–lidar SLAM pipeline that leverages lidar data and 3DGS for both pose estimation and mapping. Our approach integrates lidar points as 3D Gaussian primitives, ensuring precise scene geometry and reducing pose estimation errors caused by floating Gaussians. To enhance tracking performance, we apply regularization to Gaussian scaling, which constrains the shape of each Gaussian ellipsoid. For loop closure, we combine image similarity with lidar cloud distance to effectively detect and close loops. Our experiments demonstrate that VLGS-SLAM achieves state-of-the-art accuracy in the 3DGS-based SLAM field, outperforming many traditional SLAM algorithms</t>
+  </si>
+  <si>
+    <t>10.14358/PERS.26-00042R2</t>
+  </si>
+  <si>
+    <t>1: Institute of Automation, Chinese Academy of Sciences 2: School of Artificial Intelligence, University of Chinese Academy of Sciences 3: School of Computer Science and Technology, Zhejiang Sci-Tech University</t>
+  </si>
+  <si>
+    <t>Tu, Diantao 1, 2 ; Ma, Wenjuan 3 ; Shen, Shuhan 1, 2 ; </t>
+  </si>
+  <si>
+    <t>VLGS-SLAM: Visual–Lidar Three-Dimensional Gaussian Splatting Simultaneous Localization and Mapping</t>
+  </si>
+  <si>
+    <t>26-00042R2</t>
+  </si>
+  <si>
+    <t>cross-view localization, cross-view synthesis, view-transformation primitive</t>
+  </si>
+  <si>
+    <t>Cross-view localization and cross-view synthesis are commonly organized as separate retrieval and generation problems, although both integrate overhead imagery and ground-level visual evidence for navigation, mapping, digital twins, and immersive scene generation. This survey adopts a unified view in which both tasks are treated as instances of cross-view transfer. Their objectives differ, yet both are shaped by coupled viewpoint, scale, temporal, visibility, and sensor-domain gaps between near-nadir and ground-level observations. The survey formulates the intermediate transfer operation as the view-transformation primitive T, a cross-view transformation stage before task-specific retrieval or generation modules. In localization, T supports descriptor construction and pose-aware matching. In synthesis, it converts source observations, pose cues, layouts, geographic context, or scene supports into conditioning representations for generation. The resulting taxonomy organizes localization by the interaction between transformation and backbone and synthesis by the coupling among generation engine, conditioning representation, geographic objective, and rendering mechanism. The review further examines data sets, objectives, metrics, and protocols, linking empirical conclusions to geographic coverage, sampling density, pose metadata, sequence continuity, and metric design. Across both tasks, the analysis identifies trade-offs among geometric explicitness, scalability, data demand, generalization, photorealism, and geographic fidelity and isolates common failure modes caused by incomplete geometry, temporal drift, scale mismatch, and weak static-scene evidence. The resulting analysis motivates deployment-scale retrieval, continuous pose estimation, temporally aware supervision, multi-view consistent synthesis, geographic identity preservation, and unified discriminative-generative representations.</t>
+  </si>
+  <si>
+    <t>10.14358/PERS.26-00063R2</t>
+  </si>
+  <si>
+    <t>1: Geospatial Data Analytics Lab, The Ohio State University 2: Department of Electrical and Computer Engineering, The Ohio State University 3: Department of Civil, Environmental and Geodetic Engineering, The Ohio State University 4: Geospatial Data Analytics Lab, The Ohio State University</t>
+  </si>
+  <si>
+    <t>Xu, Ningli 1, 2 ; Liu, Hanyang 1, 3 ; Qin, Rongjun 4, 3, 2 ; </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross-view Localization and Synthesis: Data Sets, Challenges, and Opportunities </t>
+  </si>
+  <si>
+    <t>26-00063R2</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1gQZapwQD3k3HbGoF47zoHCScc70mvJc3/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1E6z65y-_NmvJ3QbxkfjzI2usEcPJi8QB/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>simultaneous localization and mapping (SLAM); Pose estimation; cubature Kalman filter; non-Gaussian noise; Gaussian manifold projection; structure-spectrum dual-domain regularization</t>
+  </si>
+  <si>
+    <t>To address the challenges of non-Gaussian process disturbances, observation contamination, and numerical degeneration of high-dimensional covariance matrices in outdoor large-scale mobile mapping and simultaneous localization and mapping (SLAM), this paper proposes a Gaussian-manifold–based structure–spectrum dual-domain regularized cubature Kalman filter, termed GM-SSDRCKF-SLAM. From an information-geometric perspective, the local approximation of the non-Gaussian posterior is formulated as a Kullback–Leibler divergence minimizing projection onto a statistical manifold. On this basis, a geometrically consistent recursive estimation framework is established by combining the tangent-space pose error modeling on the planar pose manifold. In the prediction stage, Student’s t–based local Gaussianization and L-curve–guided truncated singular value stabilization are introduced to mitigate the effects of heavy-tailed process noise and covariance spectral degeneration. In the observation stage, the Akaike Information Criterion and Bayesian Information Criterion–guided adaptive feature-landmark selection together with Student’s t robust weighting is used to jointly suppress abnormal measurements, weakly informative features, and redundant state expansion. Comparative experiments under multiple non-Gaussian noise settings are conducted on both a classical simulation environment and the Victoria Park real data set. Under severe observation contamination, GM-SSDRCKF reduces position root mean square error (RMSE) by 86.2% and 52.1% and orientation RMSE by 90.3% and 72.7%, relative to CKF-SLAM and Student’s t CKF-SLAM, respectively. Under coupled non-Gaussian disturbances, the corresponding reductions are 81.7% and 49.3% in position RMSE and 88.5% and 72.7% in orientation RMSE. In the real-world Victoria Park experiments, additional comparisons with invariant EKF-SLAM and robust GraphSLAM further demonstrate the advantage of the proposed method. Averaged over two real-data cases, GM-SSDRCKF reduces position RMSE by 85.3%, 68.2%, 70.1%, and 47.0% relative to CKF-SLAM, Student’s t CKF-SLAM, invariant EKF-SLAM, and robust GraphSLAM, respectively. The proposed method also yields shorter localization-error tails, more consistent normalized average estimation error squared behavior, and more stable covariance spectra. These results demonstrate that reliable SLAM in complex non-Gaussian environments requires the coordinated treatment of posterior approximation, geometric consistency, state-structure regulation, and covariance spectral stabilization.</t>
+  </si>
+  <si>
+    <t>10.14358/PERS.26-00039R3</t>
+  </si>
+  <si>
+    <t>Gaussian manifold projection; Pose estimation; cubature Kalman filter; non-Gaussian noise; simultaneous localization and mapping (SLAM); structure-spectrum dual-domain regularization</t>
+  </si>
+  <si>
+    <t>Xu, Hanghang; Li, Kemeng; Zhang, Hongli; Wang, Yinggang; Chen, Yijin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robust Simultaneous Localization and Mapping in Non-Gaussian Environments Using Gaussian-Manifold–Projected Structure–Spectrum Regularized Cubature Kalman Filter </t>
+  </si>
+  <si>
+    <t>26-00039R3</t>
   </si>
 </sst>
 </file>
@@ -1530,6 +1602,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1849,7 +1925,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8FD8486-47DD-4802-9EE8-87FBEF8AE4F5}">
-  <dimension ref="A1:S50"/>
+  <dimension ref="A1:S53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -3846,7 +3922,7 @@
       <c r="R49" s="23"/>
     </row>
     <row r="50" spans="1:18" ht="240" x14ac:dyDescent="0.25">
-      <c r="B50" s="15">
+      <c r="A50" s="15">
         <v>46255</v>
       </c>
       <c r="C50" s="15"/>
@@ -3885,6 +3961,131 @@
       <c r="P50" s="23"/>
       <c r="Q50" s="23"/>
       <c r="R50" s="23"/>
+    </row>
+    <row r="51" spans="1:18" ht="135" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B51" s="15"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="O51" s="5"/>
+      <c r="P51" s="24"/>
+      <c r="Q51" s="24"/>
+      <c r="R51" s="24"/>
+    </row>
+    <row r="52" spans="1:18" ht="225" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B52" s="15"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="O52" s="5"/>
+      <c r="P52" s="23"/>
+      <c r="Q52" s="23"/>
+      <c r="R52" s="23"/>
+    </row>
+    <row r="53" spans="1:18" ht="315" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B53" s="15"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="N53" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="P53" s="23"/>
+      <c r="Q53" s="23"/>
+      <c r="R53" s="23"/>
     </row>
   </sheetData>
   <autoFilter ref="E1:E13" xr:uid="{D8FD8486-47DD-4802-9EE8-87FBEF8AE4F5}"/>

--- a/26-08_August_Metadata.xlsx
+++ b/26-08_August_Metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://asprsorg-my.sharepoint.com/personal/maustin_asprs_org/Documents/PERS/2026 PERS/2026 PERS Metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="170" documentId="8_{5EE3A922-ABA0-43D0-A9B5-4D5B4955916C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F9A554C-425E-43C7-B91A-216C2A0EDFBE}"/>
+  <xr:revisionPtr revIDLastSave="173" documentId="8_{5EE3A922-ABA0-43D0-A9B5-4D5B4955916C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E1EE906-0134-4A6D-A741-7627FD9FCA80}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ED1827D4-DBB2-442E-8398-F081D1A3FEC4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="443">
   <si>
     <t>Manuscript No.</t>
   </si>
@@ -1344,6 +1344,30 @@
   </si>
   <si>
     <t>26-00039R3</t>
+  </si>
+  <si>
+    <t>Surface deformation monitoring; automatic identification; multimodal fusion; Deep Learning; Fa'er Town</t>
+  </si>
+  <si>
+    <t>Automatic detection and precise boundary delineation of surface deformation targets in complex mountainous terrain are essential for monitoring geohazards such as landslides and mining-induced subsidence. To address the low efficiency of conventional visual interpretation, the fragmented boundaries derived from single-source interferometric synthetic aperture radar (InSAR) results, and the limited capability of optical imagery to characterize deformation activity, this study proposes an InSAR-guided two-stage multi-modal recognition framework. First, small baseline subset InSAR processing was performed using Sentinel-1 ascending-track data, and candidate deformation regions characterized by negative line-of-sight (LOS) anomalies were automatically generated using robust statistical thresholds, spatial-connectivity constraints, and topographic rules. Subsequently, within the candidate regions, InSAR-derived LOS deformation velocities, Sentinel-2 optical bands and spectral indices, and digital elevation model (DEM)–derived elevation and slope information were integrated to construct a multi-channel input. Deep learning–based semantic segmentation models were then used for target recognition and precise boundary delineation. Experiments were conducted using Fa’er Town in Liupanshui City, Guizhou Province, as the source domain and Panzhou City as the geographically adjacent target domain. The results showed that the convolutional neural network + Transformer model achieved the best overall performance in the within-domain evaluation, with intersection over union (IoU), boundary F1 score, and mean symmetric distance values of 0.9716, 0.9789, and 1.225 m, respectively. The ablation experiments indicated that the fusion of InSAR, optical, and DEM data yielded the best performance, achieving precision, recall, Dice, and IoU values of 0.996, 0.996, 0.996, and 0.991, respectively. The cross-region transfer experiment between geographically adjacent domains showed that directly transferring the source-domain model to the target domain resulted in a marked performance degradation, whereas few-shot fine-tuning substantially restored the model’s recognition capability in the target domain. These findings demonstrate that the proposed method effectively integrates deformation activity, spectral–textural features, and topographic constraints, thereby providing methodological support for the automatic detection and precise boundary delineation of surface deformation targets in complex mountainous terrain.</t>
+  </si>
+  <si>
+    <t>10.14358/PERS.26-00071R2</t>
+  </si>
+  <si>
+    <t>1: Key Laboratory of Karst Georesources and Environment, Ministry of Education, Guizhou University 2: College of Resources and Environmental Engineering, Guizhou University 3: 111 Geological Team, Bureau of Geology and Mineral Exploration and Development of Guizhou Province</t>
+  </si>
+  <si>
+    <t>Li, Zengying 1, 2 ; Liang, Feng 1, 2 ; Shi, Wenbing 1, 2 ; Chen, Kuayue 1, 2 ; Xie, Jing 3 ; </t>
+  </si>
+  <si>
+    <t>Interferometric Synthetic Aperture Radar–Guided Multi-Modal Deep Learning for Surface Deformation Target Detection and Boundary Extraction in Complex Mountainous Areas</t>
+  </si>
+  <si>
+    <t>26-00071R2</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1CwfaQKtW72_e7ltfsu9DjI-UVDJ-KLPp/view?usp=drive_link</t>
   </si>
 </sst>
 </file>
@@ -1925,7 +1949,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8FD8486-47DD-4802-9EE8-87FBEF8AE4F5}">
-  <dimension ref="A1:S53"/>
+  <dimension ref="A1:S54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -4087,6 +4111,48 @@
       <c r="Q53" s="23"/>
       <c r="R53" s="23"/>
     </row>
+    <row r="54" spans="1:18" ht="300" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B54" s="15"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="O54" s="5"/>
+      <c r="P54" s="26"/>
+      <c r="Q54" s="23"/>
+      <c r="R54" s="23"/>
+    </row>
   </sheetData>
   <autoFilter ref="E1:E13" xr:uid="{D8FD8486-47DD-4802-9EE8-87FBEF8AE4F5}"/>
   <hyperlinks>
